--- a/excels/pontos_selecionados_100m.xlsx
+++ b/excels/pontos_selecionados_100m.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,28 +413,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Elevacao_deg</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Azimute_otimo_deg</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Desvio_z_resultante_m</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>Alcance_x_m</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
-          <t>Desvio_z_resultante_m</t>
+          <t>Altura_max_m</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Tempo_voo_s</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Diferenca_x_m</t>
         </is>
       </c>
     </row>
@@ -458,10 +461,19 @@
         <v>-1.35</v>
       </c>
       <c r="C2" t="n">
+        <v>4.259246773041941</v>
+      </c>
+      <c r="D2" t="n">
         <v>16796.79426326996</v>
       </c>
-      <c r="D2" t="n">
-        <v>4.259246773041941</v>
+      <c r="E2" t="n">
+        <v>5103.246457095753</v>
+      </c>
+      <c r="F2" t="n">
+        <v>62.04180900746973</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -472,10 +484,19 @@
         <v>-1.2</v>
       </c>
       <c r="C3" t="n">
+        <v>4.255394009403566</v>
+      </c>
+      <c r="D3" t="n">
         <v>16715.88633845619</v>
       </c>
-      <c r="D3" t="n">
-        <v>4.255394009403566</v>
+      <c r="E3" t="n">
+        <v>4513.638861885515</v>
+      </c>
+      <c r="F3" t="n">
+        <v>58.18687931606762</v>
+      </c>
+      <c r="G3" t="n">
+        <v>80.90792481377139</v>
       </c>
     </row>
     <row r="4">
@@ -486,10 +507,19 @@
         <v>-1.15</v>
       </c>
       <c r="C4" t="n">
+        <v>2.135880508484953</v>
+      </c>
+      <c r="D4" t="n">
         <v>16634.56347989951</v>
       </c>
-      <c r="D4" t="n">
-        <v>2.135880508484953</v>
+      <c r="E4" t="n">
+        <v>4273.205766979197</v>
+      </c>
+      <c r="F4" t="n">
+        <v>56.55230933819677</v>
+      </c>
+      <c r="G4" t="n">
+        <v>81.32285855667942</v>
       </c>
     </row>
     <row r="5">
@@ -500,10 +530,19 @@
         <v>-1.1</v>
       </c>
       <c r="C5" t="n">
+        <v>4.031470865888904</v>
+      </c>
+      <c r="D5" t="n">
         <v>16550.86121953024</v>
       </c>
-      <c r="D5" t="n">
-        <v>4.031470865888904</v>
+      <c r="E5" t="n">
+        <v>4085.6368617805</v>
+      </c>
+      <c r="F5" t="n">
+        <v>55.24901332756559</v>
+      </c>
+      <c r="G5" t="n">
+        <v>83.70226036926761</v>
       </c>
     </row>
     <row r="6">
@@ -514,10 +553,19 @@
         <v>-1.1</v>
       </c>
       <c r="C6" t="n">
+        <v>-5.927495674659212</v>
+      </c>
+      <c r="D6" t="n">
         <v>16469.30928122055</v>
       </c>
-      <c r="D6" t="n">
-        <v>-5.927495674659212</v>
+      <c r="E6" t="n">
+        <v>3933.185644058352</v>
+      </c>
+      <c r="F6" t="n">
+        <v>54.17045355785096</v>
+      </c>
+      <c r="G6" t="n">
+        <v>81.55193830969074</v>
       </c>
     </row>
     <row r="7">
@@ -528,10 +576,19 @@
         <v>-1.05</v>
       </c>
       <c r="C7" t="n">
+        <v>-0.2012194331792396</v>
+      </c>
+      <c r="D7" t="n">
         <v>16386.86407468531</v>
       </c>
-      <c r="D7" t="n">
-        <v>-0.2012194331792396</v>
+      <c r="E7" t="n">
+        <v>3798.521521781521</v>
+      </c>
+      <c r="F7" t="n">
+        <v>53.20267183735474</v>
+      </c>
+      <c r="G7" t="n">
+        <v>82.4452065352416</v>
       </c>
     </row>
     <row r="8">
@@ -542,10 +599,19 @@
         <v>-1</v>
       </c>
       <c r="C8" t="n">
+        <v>5.628372236873207</v>
+      </c>
+      <c r="D8" t="n">
         <v>16294.99491152334</v>
       </c>
-      <c r="D8" t="n">
-        <v>5.628372236873207</v>
+      <c r="E8" t="n">
+        <v>3664.726076058492</v>
+      </c>
+      <c r="F8" t="n">
+        <v>52.22650212072202</v>
+      </c>
+      <c r="G8" t="n">
+        <v>91.86916316196948</v>
       </c>
     </row>
     <row r="9">
@@ -556,10 +622,19 @@
         <v>-1</v>
       </c>
       <c r="C9" t="n">
+        <v>-1.580263971906104</v>
+      </c>
+      <c r="D9" t="n">
         <v>16206.85987954793</v>
       </c>
-      <c r="D9" t="n">
-        <v>-1.580263971906104</v>
+      <c r="E9" t="n">
+        <v>3548.415202139219</v>
+      </c>
+      <c r="F9" t="n">
+        <v>51.36556520664014</v>
+      </c>
+      <c r="G9" t="n">
+        <v>88.13503197540922</v>
       </c>
     </row>
     <row r="10">
@@ -570,10 +645,19 @@
         <v>-0.95</v>
       </c>
       <c r="C10" t="n">
+        <v>6.465059404682914</v>
+      </c>
+      <c r="D10" t="n">
         <v>16125.54964085969</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.465059404682914</v>
+      <c r="E10" t="n">
+        <v>3449.316635976558</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50.62262402694941</v>
+      </c>
+      <c r="G10" t="n">
+        <v>81.31023868824013</v>
       </c>
     </row>
     <row r="11">
@@ -584,10 +668,19 @@
         <v>-0.95</v>
       </c>
       <c r="C11" t="n">
+        <v>0.5032673726790257</v>
+      </c>
+      <c r="D11" t="n">
         <v>16038.92219837579</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.5032673726790257</v>
+      <c r="E11" t="n">
+        <v>3350.794858225556</v>
+      </c>
+      <c r="F11" t="n">
+        <v>49.87510078834129</v>
+      </c>
+      <c r="G11" t="n">
+        <v>86.62744248389936</v>
       </c>
     </row>
     <row r="12">
@@ -598,10 +691,19 @@
         <v>-0.95</v>
       </c>
       <c r="C12" t="n">
+        <v>-5.321804207223595</v>
+      </c>
+      <c r="D12" t="n">
         <v>15946.97855563895</v>
       </c>
-      <c r="D12" t="n">
-        <v>-5.321804207223595</v>
+      <c r="E12" t="n">
+        <v>3252.874888243626</v>
+      </c>
+      <c r="F12" t="n">
+        <v>49.12301619807527</v>
+      </c>
+      <c r="G12" t="n">
+        <v>91.94364273684005</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +714,19 @@
         <v>-0.9</v>
       </c>
       <c r="C13" t="n">
+        <v>3.774945510931935</v>
+      </c>
+      <c r="D13" t="n">
         <v>15866.30721468471</v>
       </c>
-      <c r="D13" t="n">
-        <v>3.774945510931935</v>
+      <c r="E13" t="n">
+        <v>3171.750553764438</v>
+      </c>
+      <c r="F13" t="n">
+        <v>48.49280027415092</v>
+      </c>
+      <c r="G13" t="n">
+        <v>80.6713409542408</v>
       </c>
     </row>
     <row r="14">
@@ -626,10 +737,19 @@
         <v>-0.9</v>
       </c>
       <c r="C14" t="n">
+        <v>-0.9513794909356375</v>
+      </c>
+      <c r="D14" t="n">
         <v>15781.95886963071</v>
       </c>
-      <c r="D14" t="n">
-        <v>-0.9513794909356375</v>
+      <c r="E14" t="n">
+        <v>3091.0750881018</v>
+      </c>
+      <c r="F14" t="n">
+        <v>47.85942197717807</v>
+      </c>
+      <c r="G14" t="n">
+        <v>84.34834505400067</v>
       </c>
     </row>
     <row r="15">
@@ -640,10 +760,19 @@
         <v>-0.9</v>
       </c>
       <c r="C15" t="n">
+        <v>-5.585317767701657</v>
+      </c>
+      <c r="D15" t="n">
         <v>15693.93977665885</v>
       </c>
-      <c r="D15" t="n">
-        <v>-5.585317767701657</v>
+      <c r="E15" t="n">
+        <v>3010.862088384093</v>
+      </c>
+      <c r="F15" t="n">
+        <v>47.22287396322883</v>
+      </c>
+      <c r="G15" t="n">
+        <v>88.01909297185921</v>
       </c>
     </row>
     <row r="16">
@@ -654,10 +783,19 @@
         <v>-0.85</v>
       </c>
       <c r="C16" t="n">
+        <v>3.49050340396784</v>
+      </c>
+      <c r="D16" t="n">
         <v>15602.2610629741</v>
       </c>
-      <c r="D16" t="n">
-        <v>3.49050340396784</v>
+      <c r="E16" t="n">
+        <v>2931.122459003042</v>
+      </c>
+      <c r="F16" t="n">
+        <v>46.58314731207951</v>
+      </c>
+      <c r="G16" t="n">
+        <v>91.67871368475062</v>
       </c>
     </row>
     <row r="17">
@@ -668,10 +806,19 @@
         <v>-0.85</v>
       </c>
       <c r="C17" t="n">
+        <v>-1.037878318541236</v>
+      </c>
+      <c r="D17" t="n">
         <v>15506.9294118208</v>
       </c>
-      <c r="D17" t="n">
-        <v>-1.037878318541236</v>
+      <c r="E17" t="n">
+        <v>2851.869278407253</v>
+      </c>
+      <c r="F17" t="n">
+        <v>45.9402204076633</v>
+      </c>
+      <c r="G17" t="n">
+        <v>95.33165115329939</v>
       </c>
     </row>
     <row r="18">
@@ -682,10 +829,19 @@
         <v>-0.85</v>
       </c>
       <c r="C18" t="n">
+        <v>-5.474464779154843</v>
+      </c>
+      <c r="D18" t="n">
         <v>15407.95248847064</v>
       </c>
-      <c r="D18" t="n">
-        <v>-5.474464779154843</v>
+      <c r="E18" t="n">
+        <v>2773.114088740647</v>
+      </c>
+      <c r="F18" t="n">
+        <v>45.29406830274415</v>
+      </c>
+      <c r="G18" t="n">
+        <v>98.97692335015927</v>
       </c>
     </row>
     <row r="19">
@@ -696,10 +852,19 @@
         <v>-0.8</v>
       </c>
       <c r="C19" t="n">
+        <v>4.41775145932391</v>
+      </c>
+      <c r="D19" t="n">
         <v>15326.15375838277</v>
       </c>
-      <c r="D19" t="n">
-        <v>4.41775145932391</v>
+      <c r="E19" t="n">
+        <v>2710.479233231903</v>
+      </c>
+      <c r="F19" t="n">
+        <v>44.77479849686937</v>
+      </c>
+      <c r="G19" t="n">
+        <v>81.79873008787035</v>
       </c>
     </row>
     <row r="20">
@@ -710,10 +875,19 @@
         <v>-0.8</v>
       </c>
       <c r="C20" t="n">
+        <v>0.9213691731316265</v>
+      </c>
+      <c r="D20" t="n">
         <v>15242.03182157639</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.9213691731316265</v>
+      <c r="E20" t="n">
+        <v>2648.179836733787</v>
+      </c>
+      <c r="F20" t="n">
+        <v>44.25341519203397</v>
+      </c>
+      <c r="G20" t="n">
+        <v>84.1219368063812</v>
       </c>
     </row>
     <row r="21">
@@ -724,10 +898,19 @@
         <v>-0.8</v>
       </c>
       <c r="C21" t="n">
+        <v>-2.516015874329639</v>
+      </c>
+      <c r="D21" t="n">
         <v>15155.58953629455</v>
       </c>
-      <c r="D21" t="n">
-        <v>-2.516015874329639</v>
+      <c r="E21" t="n">
+        <v>2586.219727373832</v>
+      </c>
+      <c r="F21" t="n">
+        <v>43.72989508424339</v>
+      </c>
+      <c r="G21" t="n">
+        <v>86.44228528183885</v>
       </c>
     </row>
     <row r="22">
@@ -738,10 +921,19 @@
         <v>-0.8</v>
       </c>
       <c r="C22" t="n">
+        <v>-5.895489208805533</v>
+      </c>
+      <c r="D22" t="n">
         <v>15066.82834195813</v>
       </c>
-      <c r="D22" t="n">
-        <v>-5.895489208805533</v>
+      <c r="E22" t="n">
+        <v>2524.603944033939</v>
+      </c>
+      <c r="F22" t="n">
+        <v>43.20420010355904</v>
+      </c>
+      <c r="G22" t="n">
+        <v>88.76119433642089</v>
       </c>
     </row>
     <row r="23">
@@ -752,10 +944,19 @@
         <v>-0.75</v>
       </c>
       <c r="C23" t="n">
+        <v>3.853207868639297</v>
+      </c>
+      <c r="D23" t="n">
         <v>14975.75301183174</v>
       </c>
-      <c r="D23" t="n">
-        <v>3.853207868639297</v>
+      <c r="E23" t="n">
+        <v>2463.34350512416</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42.67629956531349</v>
+      </c>
+      <c r="G23" t="n">
+        <v>91.07533012638851</v>
       </c>
     </row>
     <row r="24">
@@ -766,10 +967,19 @@
         <v>-0.75</v>
       </c>
       <c r="C24" t="n">
+        <v>0.5114952539834425</v>
+      </c>
+      <c r="D24" t="n">
         <v>14882.36197625329</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.5114952539834425</v>
+      <c r="E24" t="n">
+        <v>2402.439984749953</v>
+      </c>
+      <c r="F24" t="n">
+        <v>42.14615033508744</v>
+      </c>
+      <c r="G24" t="n">
+        <v>93.3910355784501</v>
       </c>
     </row>
     <row r="25">
@@ -780,10 +990,19 @@
         <v>-0.75</v>
       </c>
       <c r="C25" t="n">
+        <v>-2.771247805010726</v>
+      </c>
+      <c r="D25" t="n">
         <v>14786.65430926641</v>
       </c>
-      <c r="D25" t="n">
-        <v>-2.771247805010726</v>
+      <c r="E25" t="n">
+        <v>2341.902137125125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>41.61371026535715</v>
+      </c>
+      <c r="G25" t="n">
+        <v>95.70766698688021</v>
       </c>
     </row>
     <row r="26">
@@ -794,10 +1013,19 @@
         <v>-0.75</v>
       </c>
       <c r="C26" t="n">
+        <v>-5.995364701442992</v>
+      </c>
+      <c r="D26" t="n">
         <v>14688.62744867308</v>
       </c>
-      <c r="D26" t="n">
-        <v>-5.995364701442992</v>
+      <c r="E26" t="n">
+        <v>2281.735018696627</v>
+      </c>
+      <c r="F26" t="n">
+        <v>41.07892629931384</v>
+      </c>
+      <c r="G26" t="n">
+        <v>98.02686059333064</v>
       </c>
     </row>
     <row r="27">
@@ -808,10 +1036,19 @@
         <v>-0.7</v>
       </c>
       <c r="C27" t="n">
+        <v>3.570724072373088</v>
+      </c>
+      <c r="D27" t="n">
         <v>14588.28074982188</v>
       </c>
-      <c r="D27" t="n">
-        <v>3.570724072373088</v>
+      <c r="E27" t="n">
+        <v>2221.94457578589</v>
+      </c>
+      <c r="F27" t="n">
+        <v>40.54174683277036</v>
+      </c>
+      <c r="G27" t="n">
+        <v>100.3466988511991</v>
       </c>
     </row>
     <row r="28">
@@ -822,10 +1059,19 @@
         <v>-0.7</v>
       </c>
       <c r="C28" t="n">
+        <v>0.3771228504986021</v>
+      </c>
+      <c r="D28" t="n">
         <v>14485.60630110197</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.3771228504986021</v>
+      <c r="E28" t="n">
+        <v>2162.538413520161</v>
+      </c>
+      <c r="F28" t="n">
+        <v>40.00211044890241</v>
+      </c>
+      <c r="G28" t="n">
+        <v>102.6744487199103</v>
       </c>
     </row>
     <row r="29">
@@ -836,10 +1082,19 @@
         <v>-0.7</v>
       </c>
       <c r="C29" t="n">
+        <v>-2.75758854899307</v>
+      </c>
+      <c r="D29" t="n">
         <v>14380.59738829264</v>
       </c>
-      <c r="D29" t="n">
-        <v>-2.75758854899307</v>
+      <c r="E29" t="n">
+        <v>2103.524966652081</v>
+      </c>
+      <c r="F29" t="n">
+        <v>39.45995729525031</v>
+      </c>
+      <c r="G29" t="n">
+        <v>105.0089128093314</v>
       </c>
     </row>
     <row r="30">
@@ -850,10 +1105,19 @@
         <v>-0.7</v>
       </c>
       <c r="C30" t="n">
+        <v>-5.069525268404016</v>
+      </c>
+      <c r="D30" t="n">
         <v>14300.30240486495</v>
       </c>
-      <c r="D30" t="n">
-        <v>-5.069525268404016</v>
+      <c r="E30" t="n">
+        <v>2059.523483018067</v>
+      </c>
+      <c r="F30" t="n">
+        <v>39.05164442482756</v>
+      </c>
+      <c r="G30" t="n">
+        <v>80.29498342768966</v>
       </c>
     </row>
     <row r="31">
@@ -864,10 +1128,19 @@
         <v>-0.65</v>
       </c>
       <c r="C31" t="n">
+        <v>5.061379448383065</v>
+      </c>
+      <c r="D31" t="n">
         <v>14218.68523920398</v>
       </c>
-      <c r="D31" t="n">
-        <v>5.061379448383065</v>
+      <c r="E31" t="n">
+        <v>2015.749416120662</v>
+      </c>
+      <c r="F31" t="n">
+        <v>38.64184399839783</v>
+      </c>
+      <c r="G31" t="n">
+        <v>81.61716566096948</v>
       </c>
     </row>
     <row r="32">
@@ -878,10 +1151,19 @@
         <v>-0.65</v>
       </c>
       <c r="C32" t="n">
+        <v>2.745024130445106</v>
+      </c>
+      <c r="D32" t="n">
         <v>14135.74049398444</v>
       </c>
-      <c r="D32" t="n">
-        <v>2.745024130445106</v>
+      <c r="E32" t="n">
+        <v>1972.203157162859</v>
+      </c>
+      <c r="F32" t="n">
+        <v>38.23052434646952</v>
+      </c>
+      <c r="G32" t="n">
+        <v>82.94474521953998</v>
       </c>
     </row>
     <row r="33">
@@ -892,10 +1174,19 @@
         <v>-0.65</v>
       </c>
       <c r="C33" t="n">
+        <v>0.4626378548019731</v>
+      </c>
+      <c r="D33" t="n">
         <v>14051.45993367458</v>
       </c>
-      <c r="D33" t="n">
-        <v>0.4626378548019731</v>
+      <c r="E33" t="n">
+        <v>1928.891871530578</v>
+      </c>
+      <c r="F33" t="n">
+        <v>37.81764484099936</v>
+      </c>
+      <c r="G33" t="n">
+        <v>84.28056030986045</v>
       </c>
     </row>
     <row r="34">
@@ -906,10 +1197,19 @@
         <v>-0.65</v>
       </c>
       <c r="C34" t="n">
+        <v>-1.78560761747641</v>
+      </c>
+      <c r="D34" t="n">
         <v>13965.83720175028</v>
       </c>
-      <c r="D34" t="n">
-        <v>-1.78560761747641</v>
+      <c r="E34" t="n">
+        <v>1885.816225308809</v>
+      </c>
+      <c r="F34" t="n">
+        <v>37.40317294738062</v>
+      </c>
+      <c r="G34" t="n">
+        <v>85.62273192429893</v>
       </c>
     </row>
     <row r="35">
@@ -920,10 +1220,19 @@
         <v>-0.65</v>
       </c>
       <c r="C35" t="n">
+        <v>-3.999735219502745</v>
+      </c>
+      <c r="D35" t="n">
         <v>13878.86334381788</v>
       </c>
-      <c r="D35" t="n">
-        <v>-3.999735219502745</v>
+      <c r="E35" t="n">
+        <v>1842.97959125577</v>
+      </c>
+      <c r="F35" t="n">
+        <v>36.98706609953429</v>
+      </c>
+      <c r="G35" t="n">
+        <v>86.97385793240028</v>
       </c>
     </row>
     <row r="36">
@@ -934,10 +1243,19 @@
         <v>-0.6</v>
       </c>
       <c r="C36" t="n">
+        <v>5.855094244285363</v>
+      </c>
+      <c r="D36" t="n">
         <v>13790.52902146015</v>
       </c>
-      <c r="D36" t="n">
-        <v>5.855094244285363</v>
+      <c r="E36" t="n">
+        <v>1800.385311465513</v>
+      </c>
+      <c r="F36" t="n">
+        <v>36.56928185555581</v>
+      </c>
+      <c r="G36" t="n">
+        <v>88.33432235773034</v>
       </c>
     </row>
     <row r="37">
@@ -948,10 +1266,19 @@
         <v>-0.6</v>
       </c>
       <c r="C37" t="n">
+        <v>3.632378672011636</v>
+      </c>
+      <c r="D37" t="n">
         <v>13700.82624575568</v>
       </c>
-      <c r="D37" t="n">
-        <v>3.632378672011636</v>
+      <c r="E37" t="n">
+        <v>1758.038258494985</v>
+      </c>
+      <c r="F37" t="n">
+        <v>36.14977926322705</v>
+      </c>
+      <c r="G37" t="n">
+        <v>89.7027757044707</v>
       </c>
     </row>
     <row r="38">
@@ -962,10 +1289,19 @@
         <v>-0.6</v>
       </c>
       <c r="C38" t="n">
+        <v>1.443453778952195</v>
+      </c>
+      <c r="D38" t="n">
         <v>13609.74253091353</v>
       </c>
-      <c r="D38" t="n">
-        <v>1.443453778952195</v>
+      <c r="E38" t="n">
+        <v>1715.942031757883</v>
+      </c>
+      <c r="F38" t="n">
+        <v>35.72851178660101</v>
+      </c>
+      <c r="G38" t="n">
+        <v>91.08371484214877</v>
       </c>
     </row>
     <row r="39">
@@ -976,10 +1312,19 @@
         <v>-0.6</v>
       </c>
       <c r="C39" t="n">
+        <v>-0.7107728370437695</v>
+      </c>
+      <c r="D39" t="n">
         <v>13517.26519002583</v>
       </c>
-      <c r="D39" t="n">
-        <v>-0.7107728370437695</v>
+      <c r="E39" t="n">
+        <v>1674.10054936208</v>
+      </c>
+      <c r="F39" t="n">
+        <v>35.30542574825702</v>
+      </c>
+      <c r="G39" t="n">
+        <v>92.47734088770085</v>
       </c>
     </row>
     <row r="40">
@@ -990,10 +1335,19 @@
         <v>-0.6</v>
       </c>
       <c r="C40" t="n">
+        <v>-2.830057833466552</v>
+      </c>
+      <c r="D40" t="n">
         <v>13423.38021683469</v>
       </c>
-      <c r="D40" t="n">
-        <v>-2.830057833466552</v>
+      <c r="E40" t="n">
+        <v>1632.51824442694</v>
+      </c>
+      <c r="F40" t="n">
+        <v>34.88046315875144</v>
+      </c>
+      <c r="G40" t="n">
+        <v>93.88497319113958</v>
       </c>
     </row>
     <row r="41">
@@ -1004,10 +1358,19 @@
         <v>-0.6</v>
       </c>
       <c r="C41" t="n">
+        <v>-4.914109244006787</v>
+      </c>
+      <c r="D41" t="n">
         <v>13328.07334280396</v>
       </c>
-      <c r="D41" t="n">
-        <v>-4.914109244006787</v>
+      <c r="E41" t="n">
+        <v>1591.19910735807</v>
+      </c>
+      <c r="F41" t="n">
+        <v>34.45356748745485</v>
+      </c>
+      <c r="G41" t="n">
+        <v>95.30687403072989</v>
       </c>
     </row>
     <row r="42">
@@ -1018,10 +1381,19 @@
         <v>-0.55</v>
       </c>
       <c r="C42" t="n">
+        <v>4.584478066526374</v>
+      </c>
+      <c r="D42" t="n">
         <v>13231.32863330564</v>
       </c>
-      <c r="D42" t="n">
-        <v>4.584478066526374</v>
+      <c r="E42" t="n">
+        <v>1550.150328548559</v>
+      </c>
+      <c r="F42" t="n">
+        <v>34.02467271536216</v>
+      </c>
+      <c r="G42" t="n">
+        <v>96.74470949831993</v>
       </c>
     </row>
     <row r="43">
@@ -1032,10 +1404,19 @@
         <v>-0.55</v>
       </c>
       <c r="C43" t="n">
+        <v>2.486782467150229</v>
+      </c>
+      <c r="D43" t="n">
         <v>13133.12927778188</v>
       </c>
-      <c r="D43" t="n">
-        <v>2.486782467150229</v>
+      <c r="E43" t="n">
+        <v>1509.376213327284</v>
+      </c>
+      <c r="F43" t="n">
+        <v>33.59371679000595</v>
+      </c>
+      <c r="G43" t="n">
+        <v>98.19935552376046</v>
       </c>
     </row>
     <row r="44">
@@ -1046,10 +1427,19 @@
         <v>-0.55</v>
       </c>
       <c r="C44" t="n">
+        <v>0.4245512840326358</v>
+      </c>
+      <c r="D44" t="n">
         <v>13033.45337378938</v>
       </c>
-      <c r="D44" t="n">
-        <v>0.4245512840326358</v>
+      <c r="E44" t="n">
+        <v>1468.88250625064</v>
+      </c>
+      <c r="F44" t="n">
+        <v>33.1606220288761</v>
+      </c>
+      <c r="G44" t="n">
+        <v>99.67590399250003</v>
       </c>
     </row>
     <row r="45">
@@ -1060,10 +1450,19 @@
         <v>-0.55</v>
       </c>
       <c r="C45" t="n">
+        <v>-1.60205744602594</v>
+      </c>
+      <c r="D45" t="n">
         <v>12932.27969095165</v>
       </c>
-      <c r="D45" t="n">
-        <v>-1.60205744602594</v>
+      <c r="E45" t="n">
+        <v>1428.675065222133</v>
+      </c>
+      <c r="F45" t="n">
+        <v>32.72531382295371</v>
+      </c>
+      <c r="G45" t="n">
+        <v>101.1736828377307</v>
       </c>
     </row>
     <row r="46">
@@ -1074,10 +1473,19 @@
         <v>-0.55</v>
       </c>
       <c r="C46" t="n">
+        <v>-3.591923575164738</v>
+      </c>
+      <c r="D46" t="n">
         <v>12829.58344264573</v>
       </c>
-      <c r="D46" t="n">
-        <v>-3.591923575164738</v>
+      <c r="E46" t="n">
+        <v>1388.760621439066</v>
+      </c>
+      <c r="F46" t="n">
+        <v>32.28770581936836</v>
+      </c>
+      <c r="G46" t="n">
+        <v>102.6962483059197</v>
       </c>
     </row>
     <row r="47">
@@ -1088,10 +1496,19 @@
         <v>-0.55</v>
       </c>
       <c r="C47" t="n">
+        <v>-5.545277703840027</v>
+      </c>
+      <c r="D47" t="n">
         <v>12725.33863788674</v>
       </c>
-      <c r="D47" t="n">
-        <v>-5.545277703840027</v>
+      <c r="E47" t="n">
+        <v>1349.146305187531</v>
+      </c>
+      <c r="F47" t="n">
+        <v>31.84771210251621</v>
+      </c>
+      <c r="G47" t="n">
+        <v>104.2448047589896</v>
       </c>
     </row>
     <row r="48">
@@ -1102,10 +1519,19 @@
         <v>-0.5</v>
       </c>
       <c r="C48" t="n">
+        <v>3.551216544551662</v>
+      </c>
+      <c r="D48" t="n">
         <v>12619.51931671125</v>
       </c>
-      <c r="D48" t="n">
-        <v>3.551216544551662</v>
+      <c r="E48" t="n">
+        <v>1309.840050443743</v>
+      </c>
+      <c r="F48" t="n">
+        <v>31.40524346033787</v>
+      </c>
+      <c r="G48" t="n">
+        <v>105.8193211754897</v>
       </c>
     </row>
     <row r="49">
@@ -1116,10 +1542,19 @@
         <v>-0.5</v>
       </c>
       <c r="C49" t="n">
+        <v>1.579216598663867</v>
+      </c>
+      <c r="D49" t="n">
         <v>12512.09020717235</v>
       </c>
-      <c r="D49" t="n">
-        <v>1.579216598663867</v>
+      <c r="E49" t="n">
+        <v>1270.848400894126</v>
+      </c>
+      <c r="F49" t="n">
+        <v>30.96019236689728</v>
+      </c>
+      <c r="G49" t="n">
+        <v>107.4291095388999</v>
       </c>
     </row>
     <row r="50">
@@ -1130,10 +1565,19 @@
         <v>-0.5</v>
       </c>
       <c r="C50" t="n">
+        <v>-0.3561614038786389</v>
+      </c>
+      <c r="D50" t="n">
         <v>12403.01821589701</v>
       </c>
-      <c r="D50" t="n">
-        <v>-0.3561614038786389</v>
+      <c r="E50" t="n">
+        <v>1232.17961016151</v>
+      </c>
+      <c r="F50" t="n">
+        <v>30.51245907245294</v>
+      </c>
+      <c r="G50" t="n">
+        <v>109.0719912753411</v>
       </c>
     </row>
     <row r="51">
@@ -1144,10 +1588,19 @@
         <v>-0.5</v>
       </c>
       <c r="C51" t="n">
+        <v>-2.253384357693595</v>
+      </c>
+      <c r="D51" t="n">
         <v>12292.26260956326</v>
       </c>
-      <c r="D51" t="n">
-        <v>-2.253384357693595</v>
+      <c r="E51" t="n">
+        <v>1193.843874745351</v>
+      </c>
+      <c r="F51" t="n">
+        <v>30.06191766553227</v>
+      </c>
+      <c r="G51" t="n">
+        <v>110.7556063337488</v>
       </c>
     </row>
     <row r="52">
@@ -1158,10 +1611,19 @@
         <v>-0.5</v>
       </c>
       <c r="C52" t="n">
+        <v>-4.11243561288555</v>
+      </c>
+      <c r="D52" t="n">
         <v>12179.78436417378</v>
       </c>
-      <c r="D52" t="n">
-        <v>-4.11243561288555</v>
+      <c r="E52" t="n">
+        <v>1155.847914303483</v>
+      </c>
+      <c r="F52" t="n">
+        <v>29.60845714584479</v>
+      </c>
+      <c r="G52" t="n">
+        <v>112.4782453894804</v>
       </c>
     </row>
     <row r="53">
@@ -1172,10 +1634,19 @@
         <v>-0.45</v>
       </c>
       <c r="C53" t="n">
+        <v>4.595487713627366</v>
+      </c>
+      <c r="D53" t="n">
         <v>12065.53680835601</v>
       </c>
-      <c r="D53" t="n">
-        <v>4.595487713627366</v>
+      <c r="E53" t="n">
+        <v>1118.199058936491</v>
+      </c>
+      <c r="F53" t="n">
+        <v>29.15194083844407</v>
+      </c>
+      <c r="G53" t="n">
+        <v>114.2475558177703</v>
       </c>
     </row>
     <row r="54">
@@ -1186,10 +1657,19 @@
         <v>-0.45</v>
       </c>
       <c r="C54" t="n">
+        <v>2.713199570411613</v>
+      </c>
+      <c r="D54" t="n">
         <v>11949.46946527156</v>
       </c>
-      <c r="D54" t="n">
-        <v>2.713199570411613</v>
+      <c r="E54" t="n">
+        <v>1080.907842362779</v>
+      </c>
+      <c r="F54" t="n">
+        <v>28.69222485662517</v>
+      </c>
+      <c r="G54" t="n">
+        <v>116.067343084449</v>
       </c>
     </row>
     <row r="55">
@@ -1200,10 +1680,19 @@
         <v>-0.45</v>
       </c>
       <c r="C55" t="n">
+        <v>0.8687982180799123</v>
+      </c>
+      <c r="D55" t="n">
         <v>11831.52766062951</v>
       </c>
-      <c r="D55" t="n">
-        <v>0.8687982180799123</v>
+      <c r="E55" t="n">
+        <v>1043.984823788539</v>
+      </c>
+      <c r="F55" t="n">
+        <v>28.22916408791948</v>
+      </c>
+      <c r="G55" t="n">
+        <v>117.9418046420506</v>
       </c>
     </row>
     <row r="56">
@@ -1214,10 +1703,19 @@
         <v>-0.45</v>
       </c>
       <c r="C56" t="n">
+        <v>-0.9360437771217461</v>
+      </c>
+      <c r="D56" t="n">
         <v>11711.6494143994</v>
       </c>
-      <c r="D56" t="n">
-        <v>-0.9360437771217461</v>
+      <c r="E56" t="n">
+        <v>1007.435894984485</v>
+      </c>
+      <c r="F56" t="n">
+        <v>27.76259017757551</v>
+      </c>
+      <c r="G56" t="n">
+        <v>119.8782462301097</v>
       </c>
     </row>
     <row r="57">
@@ -1228,10 +1726,19 @@
         <v>-0.45</v>
       </c>
       <c r="C57" t="n">
+        <v>-2.117361781337574</v>
+      </c>
+      <c r="D57" t="n">
         <v>11630.62379903423</v>
       </c>
-      <c r="D57" t="n">
-        <v>-2.117361781337574</v>
+      <c r="E57" t="n">
+        <v>983.2838469788446</v>
+      </c>
+      <c r="F57" t="n">
+        <v>27.44950928561517</v>
+      </c>
+      <c r="G57" t="n">
+        <v>81.02561536516987</v>
       </c>
     </row>
     <row r="58">
@@ -1242,10 +1749,19 @@
         <v>-0.45</v>
       </c>
       <c r="C58" t="n">
+        <v>-3.280481343989699</v>
+      </c>
+      <c r="D58" t="n">
         <v>11548.68653466005</v>
       </c>
-      <c r="D58" t="n">
-        <v>-3.280481343989699</v>
+      <c r="E58" t="n">
+        <v>959.3043958005021</v>
+      </c>
+      <c r="F58" t="n">
+        <v>27.13473336366116</v>
+      </c>
+      <c r="G58" t="n">
+        <v>81.93726437418081</v>
       </c>
     </row>
     <row r="59">
@@ -1256,10 +1772,19 @@
         <v>-0.45</v>
       </c>
       <c r="C59" t="n">
+        <v>-4.425683957605107</v>
+      </c>
+      <c r="D59" t="n">
         <v>11465.81572598045</v>
       </c>
-      <c r="D59" t="n">
-        <v>-4.425683957605107</v>
+      <c r="E59" t="n">
+        <v>935.5041379873721</v>
+      </c>
+      <c r="F59" t="n">
+        <v>26.81820675050426</v>
+      </c>
+      <c r="G59" t="n">
+        <v>82.87080867959958</v>
       </c>
     </row>
     <row r="60">
@@ -1270,10 +1795,19 @@
         <v>-0.4</v>
       </c>
       <c r="C60" t="n">
+        <v>4.38016275646621</v>
+      </c>
+      <c r="D60" t="n">
         <v>11381.98890485684</v>
       </c>
-      <c r="D60" t="n">
-        <v>4.38016275646621</v>
+      <c r="E60" t="n">
+        <v>911.8829386470428</v>
+      </c>
+      <c r="F60" t="n">
+        <v>26.49987420925766</v>
+      </c>
+      <c r="G60" t="n">
+        <v>83.82682112360999</v>
       </c>
     </row>
     <row r="61">
@@ -1284,10 +1818,19 @@
         <v>-0.4</v>
       </c>
       <c r="C61" t="n">
+        <v>3.198275389280695</v>
+      </c>
+      <c r="D61" t="n">
         <v>11297.17842839612</v>
       </c>
-      <c r="D61" t="n">
-        <v>3.198275389280695</v>
+      <c r="E61" t="n">
+        <v>888.4450932140006</v>
+      </c>
+      <c r="F61" t="n">
+        <v>26.17966366649685</v>
+      </c>
+      <c r="G61" t="n">
+        <v>84.81047646071966</v>
       </c>
     </row>
     <row r="62">
@@ -1298,10 +1841,19 @@
         <v>-0.4</v>
       </c>
       <c r="C62" t="n">
+        <v>2.033972443705756</v>
+      </c>
+      <c r="D62" t="n">
         <v>11211.35741157651</v>
       </c>
-      <c r="D62" t="n">
-        <v>2.033972443705756</v>
+      <c r="E62" t="n">
+        <v>865.1929998100051</v>
+      </c>
+      <c r="F62" t="n">
+        <v>25.85751230856618</v>
+      </c>
+      <c r="G62" t="n">
+        <v>85.82101681961103</v>
       </c>
     </row>
     <row r="63">
@@ -1312,10 +1864,19 @@
         <v>-0.4</v>
       </c>
       <c r="C63" t="n">
+        <v>0.8885129896943593</v>
+      </c>
+      <c r="D63" t="n">
         <v>11124.49678958396</v>
       </c>
-      <c r="D63" t="n">
-        <v>0.8885129896943593</v>
+      <c r="E63" t="n">
+        <v>842.1310814331769</v>
+      </c>
+      <c r="F63" t="n">
+        <v>25.53335019489181</v>
+      </c>
+      <c r="G63" t="n">
+        <v>86.86062199254957</v>
       </c>
     </row>
     <row r="64">
@@ -1326,10 +1887,19 @@
         <v>-0.4</v>
       </c>
       <c r="C64" t="n">
+        <v>-0.238319516890669</v>
+      </c>
+      <c r="D64" t="n">
         <v>11036.56398083199</v>
       </c>
-      <c r="D64" t="n">
-        <v>-0.238319516890669</v>
+      <c r="E64" t="n">
+        <v>819.2620880149211</v>
+      </c>
+      <c r="F64" t="n">
+        <v>25.20709812242233</v>
+      </c>
+      <c r="G64" t="n">
+        <v>87.93280875196979</v>
       </c>
     </row>
     <row r="65">
@@ -1340,10 +1910,19 @@
         <v>-0.4</v>
       </c>
       <c r="C65" t="n">
+        <v>-1.34659256244324</v>
+      </c>
+      <c r="D65" t="n">
         <v>10947.5270045009</v>
       </c>
-      <c r="D65" t="n">
-        <v>-1.34659256244324</v>
+      <c r="E65" t="n">
+        <v>796.5905435038306</v>
+      </c>
+      <c r="F65" t="n">
+        <v>24.87868332114846</v>
+      </c>
+      <c r="G65" t="n">
+        <v>89.03697633109005</v>
       </c>
     </row>
     <row r="66">
@@ -1354,10 +1933,19 @@
         <v>-0.4</v>
       </c>
       <c r="C66" t="n">
+        <v>-2.435528393449838</v>
+      </c>
+      <c r="D66" t="n">
         <v>10857.34900861266</v>
       </c>
-      <c r="D66" t="n">
-        <v>-2.435528393449838</v>
+      <c r="E66" t="n">
+        <v>774.1178758863763</v>
+      </c>
+      <c r="F66" t="n">
+        <v>24.54801877258614</v>
+      </c>
+      <c r="G66" t="n">
+        <v>90.17799588823982</v>
       </c>
     </row>
     <row r="67">
@@ -1368,10 +1956,19 @@
         <v>-0.4</v>
       </c>
       <c r="C67" t="n">
+        <v>-3.50489004440469</v>
+      </c>
+      <c r="D67" t="n">
         <v>10765.99201385815</v>
       </c>
-      <c r="D67" t="n">
-        <v>-3.50489004440469</v>
+      <c r="E67" t="n">
+        <v>751.8495266029848</v>
+      </c>
+      <c r="F67" t="n">
+        <v>24.21501998099641</v>
+      </c>
+      <c r="G67" t="n">
+        <v>91.35699475451111</v>
       </c>
     </row>
     <row r="68">
@@ -1382,10 +1979,19 @@
         <v>-0.4</v>
       </c>
       <c r="C68" t="n">
+        <v>-4.55459083978347</v>
+      </c>
+      <c r="D68" t="n">
         <v>10673.41563643679</v>
       </c>
-      <c r="D68" t="n">
-        <v>-4.55459083978347</v>
+      <c r="E68" t="n">
+        <v>729.7882850797457</v>
+      </c>
+      <c r="F68" t="n">
+        <v>23.87959735763824</v>
+      </c>
+      <c r="G68" t="n">
+        <v>92.57637742135921</v>
       </c>
     </row>
     <row r="69">
@@ -1396,10 +2002,19 @@
         <v>-0.35</v>
       </c>
       <c r="C69" t="n">
+        <v>3.648105157780158</v>
+      </c>
+      <c r="D69" t="n">
         <v>10579.57536230315</v>
       </c>
-      <c r="D69" t="n">
-        <v>3.648105157780158</v>
+      <c r="E69" t="n">
+        <v>707.9376448122672</v>
+      </c>
+      <c r="F69" t="n">
+        <v>23.54165037443324</v>
+      </c>
+      <c r="G69" t="n">
+        <v>93.84027413363947</v>
       </c>
     </row>
     <row r="70">
@@ -1410,10 +2025,19 @@
         <v>-0.35</v>
       </c>
       <c r="C70" t="n">
+        <v>2.555894534778735</v>
+      </c>
+      <c r="D70" t="n">
         <v>10484.42358713199</v>
       </c>
-      <c r="D70" t="n">
-        <v>2.555894534778735</v>
+      <c r="E70" t="n">
+        <v>686.3032174246957</v>
+      </c>
+      <c r="F70" t="n">
+        <v>23.20107990222005</v>
+      </c>
+      <c r="G70" t="n">
+        <v>95.1517751711599</v>
       </c>
     </row>
     <row r="71">
@@ -1424,10 +2048,19 @@
         <v>-0.35</v>
       </c>
       <c r="C71" t="n">
+        <v>1.483515204545136</v>
+      </c>
+      <c r="D71" t="n">
         <v>10387.909489213</v>
       </c>
-      <c r="D71" t="n">
-        <v>1.483515204545136</v>
+      <c r="E71" t="n">
+        <v>664.8865737792597</v>
+      </c>
+      <c r="F71" t="n">
+        <v>22.85778004141448</v>
+      </c>
+      <c r="G71" t="n">
+        <v>96.51409791899096</v>
       </c>
     </row>
     <row r="72">
@@ -1438,10 +2071,19 @@
         <v>-0.35</v>
       </c>
       <c r="C72" t="n">
+        <v>0.4311807241951373</v>
+      </c>
+      <c r="D72" t="n">
         <v>10289.9772848487</v>
       </c>
-      <c r="D72" t="n">
-        <v>0.4311807241951373</v>
+      <c r="E72" t="n">
+        <v>643.694128040276</v>
+      </c>
+      <c r="F72" t="n">
+        <v>22.51163609407135</v>
+      </c>
+      <c r="G72" t="n">
+        <v>97.93220436430056</v>
       </c>
     </row>
     <row r="73">
@@ -1452,10 +2094,19 @@
         <v>-0.35</v>
       </c>
       <c r="C73" t="n">
+        <v>-0.6007101106425999</v>
+      </c>
+      <c r="D73" t="n">
         <v>10190.56871584911</v>
       </c>
-      <c r="D73" t="n">
-        <v>-0.6007101106425999</v>
+      <c r="E73" t="n">
+        <v>622.7277578375549</v>
+      </c>
+      <c r="F73" t="n">
+        <v>22.16253427078185</v>
+      </c>
+      <c r="G73" t="n">
+        <v>99.40856899958999</v>
       </c>
     </row>
     <row r="74">
@@ -1466,10 +2117,19 @@
         <v>-0.35</v>
       </c>
       <c r="C74" t="n">
+        <v>-1.612282704879326</v>
+      </c>
+      <c r="D74" t="n">
         <v>10089.62014319245</v>
       </c>
-      <c r="D74" t="n">
-        <v>-1.612282704879326</v>
+      <c r="E74" t="n">
+        <v>601.9947611477943</v>
+      </c>
+      <c r="F74" t="n">
+        <v>21.81035284178521</v>
+      </c>
+      <c r="G74" t="n">
+        <v>100.94857265666</v>
       </c>
     </row>
     <row r="75">
@@ -1480,10 +2140,19 @@
         <v>-0.35</v>
       </c>
       <c r="C75" t="n">
+        <v>-2.602332155054871</v>
+      </c>
+      <c r="D75" t="n">
         <v>9987.062909827922</v>
       </c>
-      <c r="D75" t="n">
-        <v>-2.602332155054871</v>
+      <c r="E75" t="n">
+        <v>581.4968187340206</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.45496501487806</v>
+      </c>
+      <c r="G75" t="n">
+        <v>102.5572333645268</v>
       </c>
     </row>
     <row r="76">
@@ -1494,10 +2163,19 @@
         <v>-0.35</v>
       </c>
       <c r="C76" t="n">
+        <v>-3.570752591448064</v>
+      </c>
+      <c r="D76" t="n">
         <v>9882.821720665865</v>
       </c>
-      <c r="D76" t="n">
-        <v>-3.570752591448064</v>
+      <c r="E76" t="n">
+        <v>561.2396376621803</v>
+      </c>
+      <c r="F76" t="n">
+        <v>21.09623550322206</v>
+      </c>
+      <c r="G76" t="n">
+        <v>104.2411891620577</v>
       </c>
     </row>
     <row r="77">
@@ -1508,10 +2186,19 @@
         <v>-0.3</v>
       </c>
       <c r="C77" t="n">
+        <v>4.014802291498402</v>
+      </c>
+      <c r="D77" t="n">
         <v>9776.817613885454</v>
       </c>
-      <c r="D77" t="n">
-        <v>4.014802291498402</v>
+      <c r="E77" t="n">
+        <v>541.2284279624088</v>
+      </c>
+      <c r="F77" t="n">
+        <v>20.73403240399482</v>
+      </c>
+      <c r="G77" t="n">
+        <v>106.0041067804104</v>
       </c>
     </row>
     <row r="78">
@@ -1522,10 +2209,19 @@
         <v>-0.3</v>
       </c>
       <c r="C78" t="n">
+        <v>2.996776707272784</v>
+      </c>
+      <c r="D78" t="n">
         <v>9668.962042535059</v>
       </c>
-      <c r="D78" t="n">
-        <v>2.996776707272784</v>
+      <c r="E78" t="n">
+        <v>521.467330241518</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20.36820955532499</v>
+      </c>
+      <c r="G78" t="n">
+        <v>107.8555713503956</v>
       </c>
     </row>
     <row r="79">
@@ -1536,10 +2232,19 @@
         <v>-0.3</v>
       </c>
       <c r="C79" t="n">
+        <v>2.000208270203115</v>
+      </c>
+      <c r="D79" t="n">
         <v>9559.163179099791</v>
       </c>
-      <c r="D79" t="n">
-        <v>2.000208270203115</v>
+      <c r="E79" t="n">
+        <v>501.960223468737</v>
+      </c>
+      <c r="F79" t="n">
+        <v>19.99863624833661</v>
+      </c>
+      <c r="G79" t="n">
+        <v>109.7988634352678</v>
       </c>
     </row>
     <row r="80">
@@ -1550,10 +2255,19 @@
         <v>-0.3</v>
       </c>
       <c r="C80" t="n">
+        <v>1.0253985594432</v>
+      </c>
+      <c r="D80" t="n">
         <v>9447.317243079788</v>
       </c>
-      <c r="D80" t="n">
-        <v>1.0253985594432</v>
+      <c r="E80" t="n">
+        <v>482.7132245564842</v>
+      </c>
+      <c r="F80" t="n">
+        <v>19.62516560606614</v>
+      </c>
+      <c r="G80" t="n">
+        <v>111.8459360200031</v>
       </c>
     </row>
     <row r="81">
@@ -1564,10 +2278,19 @@
         <v>-0.3</v>
       </c>
       <c r="C81" t="n">
+        <v>0.0732307398422239</v>
+      </c>
+      <c r="D81" t="n">
         <v>9333.316634387531</v>
       </c>
-      <c r="D81" t="n">
-        <v>0.0732307398422239</v>
+      <c r="E81" t="n">
+        <v>463.7324615159224</v>
+      </c>
+      <c r="F81" t="n">
+        <v>19.24767016429783</v>
+      </c>
+      <c r="G81" t="n">
+        <v>114.0006086922567</v>
       </c>
     </row>
     <row r="82">
@@ -1578,10 +2301,19 @@
         <v>-0.3</v>
       </c>
       <c r="C82" t="n">
+        <v>-0.8563683386120324</v>
+      </c>
+      <c r="D82" t="n">
         <v>9217.040069255421</v>
       </c>
-      <c r="D82" t="n">
-        <v>-0.8563683386120324</v>
+      <c r="E82" t="n">
+        <v>445.0216012204139</v>
+      </c>
+      <c r="F82" t="n">
+        <v>18.86601519028108</v>
+      </c>
+      <c r="G82" t="n">
+        <v>116.2765651321097</v>
       </c>
     </row>
     <row r="83">
@@ -1592,10 +2324,19 @@
         <v>-0.3</v>
       </c>
       <c r="C83" t="n">
+        <v>-1.762595038745569</v>
+      </c>
+      <c r="D83" t="n">
         <v>9098.361738352298</v>
       </c>
-      <c r="D83" t="n">
-        <v>-1.762595038745569</v>
+      <c r="E83" t="n">
+        <v>426.5863074440577</v>
+      </c>
+      <c r="F83" t="n">
+        <v>18.4800977919888</v>
+      </c>
+      <c r="G83" t="n">
+        <v>118.6783309031234</v>
       </c>
     </row>
     <row r="84">
@@ -1606,10 +2347,19 @@
         <v>-0.3</v>
       </c>
       <c r="C84" t="n">
+        <v>-2.644360922537579</v>
+      </c>
+      <c r="D84" t="n">
         <v>8977.14424568934</v>
       </c>
-      <c r="D84" t="n">
-        <v>-2.644360922537579</v>
+      <c r="E84" t="n">
+        <v>408.4330874441303</v>
+      </c>
+      <c r="F84" t="n">
+        <v>18.08983401803004</v>
+      </c>
+      <c r="G84" t="n">
+        <v>121.2174926629577</v>
       </c>
     </row>
     <row r="85">
@@ -1620,10 +2370,19 @@
         <v>-0.3</v>
       </c>
       <c r="C85" t="n">
+        <v>-3.50098738385682</v>
+      </c>
+      <c r="D85" t="n">
         <v>8853.241354828637</v>
       </c>
-      <c r="D85" t="n">
-        <v>-3.50098738385682</v>
+      <c r="E85" t="n">
+        <v>390.5671076807021</v>
+      </c>
+      <c r="F85" t="n">
+        <v>17.69518145543642</v>
+      </c>
+      <c r="G85" t="n">
+        <v>123.9028908607033</v>
       </c>
     </row>
     <row r="86">
@@ -1634,10 +2393,19 @@
         <v>-0.25</v>
       </c>
       <c r="C86" t="n">
+        <v>3.283069310771193</v>
+      </c>
+      <c r="D86" t="n">
         <v>8726.497291465312</v>
       </c>
-      <c r="D86" t="n">
-        <v>3.283069310771193</v>
+      <c r="E86" t="n">
+        <v>372.9936563804126</v>
+      </c>
+      <c r="F86" t="n">
+        <v>17.29614865901936</v>
+      </c>
+      <c r="G86" t="n">
+        <v>126.744063363325</v>
       </c>
     </row>
     <row r="87">
@@ -1648,10 +2416,19 @@
         <v>-0.25</v>
       </c>
       <c r="C87" t="n">
+        <v>2.365900617596731</v>
+      </c>
+      <c r="D87" t="n">
         <v>8596.754968110961</v>
       </c>
-      <c r="D87" t="n">
-        <v>2.365900617596731</v>
+      <c r="E87" t="n">
+        <v>355.7194796478732</v>
+      </c>
+      <c r="F87" t="n">
+        <v>16.8928310066133</v>
+      </c>
+      <c r="G87" t="n">
+        <v>129.7423233543504</v>
       </c>
     </row>
     <row r="88">
@@ -1662,10 +2439,19 @@
         <v>-0.25</v>
       </c>
       <c r="C88" t="n">
+        <v>1.473554755309755</v>
+      </c>
+      <c r="D88" t="n">
         <v>8463.848125055152</v>
       </c>
-      <c r="D88" t="n">
-        <v>1.473554755309755</v>
+      <c r="E88" t="n">
+        <v>338.7514348083193</v>
+      </c>
+      <c r="F88" t="n">
+        <v>16.48538579247939</v>
+      </c>
+      <c r="G88" t="n">
+        <v>132.9068430558091</v>
       </c>
     </row>
     <row r="89">
@@ -1676,10 +2462,19 @@
         <v>-0.25</v>
       </c>
       <c r="C89" t="n">
+        <v>1.037084240890432</v>
+      </c>
+      <c r="D89" t="n">
         <v>8396.156169315254</v>
       </c>
-      <c r="D89" t="n">
-        <v>1.037084240890432</v>
+      <c r="E89" t="n">
+        <v>330.3844436719303</v>
+      </c>
+      <c r="F89" t="n">
+        <v>16.2801846072485</v>
+      </c>
+      <c r="G89" t="n">
+        <v>67.69195573989782</v>
       </c>
     </row>
     <row r="90">
@@ -1690,10 +2485,19 @@
         <v>-0.25</v>
       </c>
       <c r="C90" t="n">
+        <v>0.6078393081440275</v>
+      </c>
+      <c r="D90" t="n">
         <v>8327.610768055585</v>
       </c>
-      <c r="D90" t="n">
-        <v>0.6078393081440275</v>
+      <c r="E90" t="n">
+        <v>322.0958279937965</v>
+      </c>
+      <c r="F90" t="n">
+        <v>16.07403905039158</v>
+      </c>
+      <c r="G90" t="n">
+        <v>68.54540125966923</v>
       </c>
     </row>
     <row r="91">
@@ -1704,10 +2508,19 @@
         <v>-0.25</v>
       </c>
       <c r="C91" t="n">
+        <v>0.1851031615923075</v>
+      </c>
+      <c r="D91" t="n">
         <v>8258.192332956163</v>
       </c>
-      <c r="D91" t="n">
-        <v>0.1851031615923075</v>
+      <c r="E91" t="n">
+        <v>313.8869286217738</v>
+      </c>
+      <c r="F91" t="n">
+        <v>15.86698378612526</v>
+      </c>
+      <c r="G91" t="n">
+        <v>69.41843509942191</v>
       </c>
     </row>
     <row r="92">
@@ -1718,10 +2531,19 @@
         <v>-0.25</v>
       </c>
       <c r="C92" t="n">
+        <v>-0.2304083976772133</v>
+      </c>
+      <c r="D92" t="n">
         <v>8187.881043599981</v>
       </c>
-      <c r="D92" t="n">
-        <v>-0.2304083976772133</v>
+      <c r="E92" t="n">
+        <v>305.7587608543312</v>
+      </c>
+      <c r="F92" t="n">
+        <v>15.65904961909916</v>
+      </c>
+      <c r="G92" t="n">
+        <v>70.31128935618199</v>
       </c>
     </row>
     <row r="93">
@@ -1732,10 +2554,19 @@
         <v>-0.25</v>
       </c>
       <c r="C93" t="n">
+        <v>-0.638688023343672</v>
+      </c>
+      <c r="D93" t="n">
         <v>8116.655844571165</v>
       </c>
-      <c r="D93" t="n">
-        <v>-0.638688023343672</v>
+      <c r="E93" t="n">
+        <v>297.7120764889744</v>
+      </c>
+      <c r="F93" t="n">
+        <v>15.45025978098895</v>
+      </c>
+      <c r="G93" t="n">
+        <v>71.22519902881595</v>
       </c>
     </row>
     <row r="94">
@@ -1746,10 +2577,19 @@
         <v>-0.25</v>
       </c>
       <c r="C94" t="n">
+        <v>-1.039643801425128</v>
+      </c>
+      <c r="D94" t="n">
         <v>8044.498213040877</v>
       </c>
-      <c r="D94" t="n">
-        <v>-1.039643801425128</v>
+      <c r="E94" t="n">
+        <v>289.7477191749576</v>
+      </c>
+      <c r="F94" t="n">
+        <v>15.24064071878504</v>
+      </c>
+      <c r="G94" t="n">
+        <v>72.1576315302882</v>
       </c>
     </row>
     <row r="95">
@@ -1760,10 +2600,19 @@
         <v>-0.25</v>
       </c>
       <c r="C95" t="n">
+        <v>-1.432890816038728</v>
+      </c>
+      <c r="D95" t="n">
         <v>7971.388099929775</v>
       </c>
-      <c r="D95" t="n">
-        <v>-1.432890816038728</v>
+      <c r="E95" t="n">
+        <v>281.8665698204761</v>
+      </c>
+      <c r="F95" t="n">
+        <v>15.03020841574768</v>
+      </c>
+      <c r="G95" t="n">
+        <v>73.11011311110178</v>
       </c>
     </row>
     <row r="96">
@@ -1774,10 +2623,19 @@
         <v>-0.25</v>
       </c>
       <c r="C96" t="n">
+        <v>-1.81910121516798</v>
+      </c>
+      <c r="D96" t="n">
         <v>7897.304857099662</v>
       </c>
-      <c r="D96" t="n">
-        <v>-1.81910121516798</v>
+      <c r="E96" t="n">
+        <v>274.0695016664031</v>
+      </c>
+      <c r="F96" t="n">
+        <v>14.81897141578585</v>
+      </c>
+      <c r="G96" t="n">
+        <v>74.0832428301137</v>
       </c>
     </row>
     <row r="97">
@@ -1788,10 +2646,19 @@
         <v>-0.25</v>
       </c>
       <c r="C97" t="n">
+        <v>-2.197169750874639</v>
+      </c>
+      <c r="D97" t="n">
         <v>7822.229958833063</v>
       </c>
-      <c r="D97" t="n">
-        <v>-2.197169750874639</v>
+      <c r="E97" t="n">
+        <v>266.3581228068016</v>
+      </c>
+      <c r="F97" t="n">
+        <v>14.60693830190459</v>
+      </c>
+      <c r="G97" t="n">
+        <v>75.07489826659821</v>
       </c>
     </row>
     <row r="98">
@@ -1802,10 +2669,19 @@
         <v>-0.25</v>
       </c>
       <c r="C98" t="n">
+        <v>-2.567169176703327</v>
+      </c>
+      <c r="D98" t="n">
         <v>7746.141435516013</v>
       </c>
-      <c r="D98" t="n">
-        <v>-2.567169176703327</v>
+      <c r="E98" t="n">
+        <v>258.732771885782</v>
+      </c>
+      <c r="F98" t="n">
+        <v>14.39410219912586</v>
+      </c>
+      <c r="G98" t="n">
+        <v>76.0885233170502</v>
       </c>
     </row>
     <row r="99">
@@ -1816,10 +2692,19 @@
         <v>-0.25</v>
       </c>
       <c r="C99" t="n">
+        <v>-2.929085388329228</v>
+      </c>
+      <c r="D99" t="n">
         <v>7669.017456777929</v>
       </c>
-      <c r="D99" t="n">
-        <v>-2.929085388329228</v>
+      <c r="E99" t="n">
+        <v>251.1942960833083</v>
+      </c>
+      <c r="F99" t="n">
+        <v>14.18045281403742</v>
+      </c>
+      <c r="G99" t="n">
+        <v>77.12397873808459</v>
       </c>
     </row>
     <row r="100">
@@ -1830,10 +2715,19 @@
         <v>-0.25</v>
       </c>
       <c r="C100" t="n">
+        <v>-3.282968654463472</v>
+      </c>
+      <c r="D100" t="n">
         <v>7590.838670877972</v>
       </c>
-      <c r="D100" t="n">
-        <v>-3.282968654463472</v>
+      <c r="E100" t="n">
+        <v>243.7440485582583</v>
+      </c>
+      <c r="F100" t="n">
+        <v>13.96598420576261</v>
+      </c>
+      <c r="G100" t="n">
+        <v>78.17878589995689</v>
       </c>
     </row>
     <row r="101">
@@ -1844,10 +2738,19 @@
         <v>-0.2</v>
       </c>
       <c r="C101" t="n">
+        <v>2.927047028674192</v>
+      </c>
+      <c r="D101" t="n">
         <v>7511.578292598958</v>
       </c>
-      <c r="D101" t="n">
-        <v>2.927047028674192</v>
+      <c r="E101" t="n">
+        <v>236.3828177021425</v>
+      </c>
+      <c r="F101" t="n">
+        <v>13.75067000943479</v>
+      </c>
+      <c r="G101" t="n">
+        <v>79.26037827901382</v>
       </c>
     </row>
     <row r="102">
@@ -1858,10 +2761,19 @@
         <v>-0.2</v>
       </c>
       <c r="C102" t="n">
+        <v>2.520151136518941</v>
+      </c>
+      <c r="D102" t="n">
         <v>7431.215298936985</v>
       </c>
-      <c r="D102" t="n">
-        <v>2.520151136518941</v>
+      <c r="E102" t="n">
+        <v>229.1117601010025</v>
+      </c>
+      <c r="F102" t="n">
+        <v>13.53450465045351</v>
+      </c>
+      <c r="G102" t="n">
+        <v>80.36299366197272</v>
       </c>
     </row>
     <row r="103">
@@ -1872,10 +2784,19 @@
         <v>-0.2</v>
       </c>
       <c r="C103" t="n">
+        <v>2.121191061476836</v>
+      </c>
+      <c r="D103" t="n">
         <v>7349.724698065353</v>
       </c>
-      <c r="D103" t="n">
-        <v>2.121191061476836</v>
+      <c r="E103" t="n">
+        <v>221.9322925813902</v>
+      </c>
+      <c r="F103" t="n">
+        <v>13.31747692876147</v>
+      </c>
+      <c r="G103" t="n">
+        <v>81.49060087163252</v>
       </c>
     </row>
     <row r="104">
@@ -1886,10 +2807,19 @@
         <v>-0.2</v>
       </c>
       <c r="C104" t="n">
+        <v>1.72977757310387</v>
+      </c>
+      <c r="D104" t="n">
         <v>7267.079772558662</v>
       </c>
-      <c r="D104" t="n">
-        <v>1.72977757310387</v>
+      <c r="E104" t="n">
+        <v>214.8444566150639</v>
+      </c>
+      <c r="F104" t="n">
+        <v>13.09957771556299</v>
+      </c>
+      <c r="G104" t="n">
+        <v>82.64492550669092</v>
       </c>
     </row>
     <row r="105">
@@ -1900,10 +2830,19 @@
         <v>-0.2</v>
       </c>
       <c r="C105" t="n">
+        <v>1.34652205716558</v>
+      </c>
+      <c r="D105" t="n">
         <v>7183.255083496055</v>
       </c>
-      <c r="D105" t="n">
-        <v>1.34652205716558</v>
+      <c r="E105" t="n">
+        <v>207.8505166049315</v>
+      </c>
+      <c r="F105" t="n">
+        <v>12.8808073529594</v>
+      </c>
+      <c r="G105" t="n">
+        <v>83.82468906260692</v>
       </c>
     </row>
     <row r="106">
@@ -1914,10 +2853,19 @@
         <v>-0.2</v>
       </c>
       <c r="C106" t="n">
+        <v>0.9717855921662497</v>
+      </c>
+      <c r="D106" t="n">
         <v>7098.223338337014</v>
       </c>
-      <c r="D106" t="n">
-        <v>0.9717855921662497</v>
+      <c r="E106" t="n">
+        <v>200.9508634340758</v>
+      </c>
+      <c r="F106" t="n">
+        <v>12.6611663482256</v>
+      </c>
+      <c r="G106" t="n">
+        <v>85.03174515904084</v>
       </c>
     </row>
     <row r="107">
@@ -1928,10 +2876,19 @@
         <v>-0.2</v>
       </c>
       <c r="C107" t="n">
+        <v>0.6052779367794384</v>
+      </c>
+      <c r="D107" t="n">
         <v>7011.95835001874</v>
       </c>
-      <c r="D107" t="n">
-        <v>0.6052779367794384</v>
+      <c r="E107" t="n">
+        <v>194.147010618707</v>
+      </c>
+      <c r="F107" t="n">
+        <v>12.4406610440362</v>
+      </c>
+      <c r="G107" t="n">
+        <v>86.26498831827394</v>
       </c>
     </row>
     <row r="108">
@@ -1942,10 +2899,19 @@
         <v>-0.2</v>
       </c>
       <c r="C108" t="n">
+        <v>0.2474810300548451</v>
+      </c>
+      <c r="D108" t="n">
         <v>6924.431098310041</v>
       </c>
-      <c r="D108" t="n">
-        <v>0.2474810300548451</v>
+      <c r="E108" t="n">
+        <v>187.4402817757905</v>
+      </c>
+      <c r="F108" t="n">
+        <v>12.21929293831797</v>
+      </c>
+      <c r="G108" t="n">
+        <v>87.52725170869871</v>
       </c>
     </row>
     <row r="109">
@@ -1956,10 +2922,19 @@
         <v>-0.2</v>
       </c>
       <c r="C109" t="n">
+        <v>-0.1015668620361421</v>
+      </c>
+      <c r="D109" t="n">
         <v>6835.614890247147</v>
       </c>
-      <c r="D109" t="n">
-        <v>-0.1015668620361421</v>
+      <c r="E109" t="n">
+        <v>180.831087039003</v>
+      </c>
+      <c r="F109" t="n">
+        <v>11.99707063944993</v>
+      </c>
+      <c r="G109" t="n">
+        <v>88.81620806289448</v>
       </c>
     </row>
     <row r="110">
@@ -1970,10 +2945,19 @@
         <v>-0.2</v>
       </c>
       <c r="C110" t="n">
+        <v>-0.4415734302168248</v>
+      </c>
+      <c r="D110" t="n">
         <v>6745.480669747007</v>
       </c>
-      <c r="D110" t="n">
-        <v>-0.4415734302168248</v>
+      <c r="E110" t="n">
+        <v>174.3209449313028</v>
+      </c>
+      <c r="F110" t="n">
+        <v>11.77399775860366</v>
+      </c>
+      <c r="G110" t="n">
+        <v>90.13422050014015</v>
       </c>
     </row>
     <row r="111">
@@ -1984,10 +2968,19 @@
         <v>-0.2</v>
       </c>
       <c r="C111" t="n">
+        <v>-0.7721891964874017</v>
+      </c>
+      <c r="D111" t="n">
         <v>6653.999566901242</v>
       </c>
-      <c r="D111" t="n">
-        <v>-0.7721891964874017</v>
+      <c r="E111" t="n">
+        <v>167.9112759785248</v>
+      </c>
+      <c r="F111" t="n">
+        <v>11.55007876884865</v>
+      </c>
+      <c r="G111" t="n">
+        <v>91.48110284576433</v>
       </c>
     </row>
     <row r="112">
@@ -1998,10 +2991,19 @@
         <v>-0.2</v>
       </c>
       <c r="C112" t="n">
+        <v>-1.0932400169257</v>
+      </c>
+      <c r="D112" t="n">
         <v>6561.144886429764</v>
       </c>
-      <c r="D112" t="n">
-        <v>-1.0932400169257</v>
+      <c r="E112" t="n">
+        <v>161.6037484052269</v>
+      </c>
+      <c r="F112" t="n">
+        <v>11.32532384396263</v>
+      </c>
+      <c r="G112" t="n">
+        <v>92.85468047147879</v>
       </c>
     </row>
     <row r="113">
@@ -2012,10 +3014,19 @@
         <v>-0.2</v>
       </c>
       <c r="C113" t="n">
+        <v>-1.404660750981126</v>
+      </c>
+      <c r="D113" t="n">
         <v>6466.882488998178</v>
       </c>
-      <c r="D113" t="n">
-        <v>-1.404660750981126</v>
+      <c r="E113" t="n">
+        <v>155.3993261581959</v>
+      </c>
+      <c r="F113" t="n">
+        <v>11.09972479290458</v>
+      </c>
+      <c r="G113" t="n">
+        <v>94.26239743158567</v>
       </c>
     </row>
     <row r="114">
@@ -2026,10 +3037,19 @@
         <v>-0.2</v>
       </c>
       <c r="C114" t="n">
+        <v>-1.705995798398143</v>
+      </c>
+      <c r="D114" t="n">
         <v>6371.187051317013</v>
       </c>
-      <c r="D114" t="n">
-        <v>-1.705995798398143</v>
+      <c r="E114" t="n">
+        <v>149.2988882425298</v>
+      </c>
+      <c r="F114" t="n">
+        <v>10.87329473718314</v>
+      </c>
+      <c r="G114" t="n">
+        <v>95.69543768116455</v>
       </c>
     </row>
     <row r="115">
@@ -2040,10 +3060,19 @@
         <v>-0.2</v>
       </c>
       <c r="C115" t="n">
+        <v>-1.996928756821923</v>
+      </c>
+      <c r="D115" t="n">
         <v>6274.026652581302</v>
       </c>
-      <c r="D115" t="n">
-        <v>-1.996928756821923</v>
+      <c r="E115" t="n">
+        <v>143.3034587864124</v>
+      </c>
+      <c r="F115" t="n">
+        <v>10.6460312037986</v>
+      </c>
+      <c r="G115" t="n">
+        <v>97.16039873571117</v>
       </c>
     </row>
     <row r="116">
@@ -2054,10 +3083,19 @@
         <v>-0.2</v>
       </c>
       <c r="C116" t="n">
+        <v>-2.277242205203299</v>
+      </c>
+      <c r="D116" t="n">
         <v>6175.371067630682</v>
       </c>
-      <c r="D116" t="n">
-        <v>-2.277242205203299</v>
+      <c r="E116" t="n">
+        <v>137.4154032811582</v>
+      </c>
+      <c r="F116" t="n">
+        <v>10.41793615328789</v>
+      </c>
+      <c r="G116" t="n">
+        <v>98.65558495062032</v>
       </c>
     </row>
     <row r="117">
@@ -2068,10 +3106,19 @@
         <v>-0.2</v>
       </c>
       <c r="C117" t="n">
+        <v>-2.546687783230694</v>
+      </c>
+      <c r="D117" t="n">
         <v>6075.189388370789</v>
       </c>
-      <c r="D117" t="n">
-        <v>-2.546687783230694</v>
+      <c r="E117" t="n">
+        <v>131.6364363934352</v>
+      </c>
+      <c r="F117" t="n">
+        <v>10.189010851049</v>
+      </c>
+      <c r="G117" t="n">
+        <v>100.1816792598929</v>
       </c>
     </row>
     <row r="118">
@@ -2082,10 +3129,19 @@
         <v>-0.15</v>
       </c>
       <c r="C118" t="n">
+        <v>2.407812484209469</v>
+      </c>
+      <c r="D118" t="n">
         <v>5973.44896028665</v>
       </c>
-      <c r="D118" t="n">
-        <v>2.407812484209469</v>
+      <c r="E118" t="n">
+        <v>125.9674462468292</v>
+      </c>
+      <c r="F118" t="n">
+        <v>9.959253015787075</v>
+      </c>
+      <c r="G118" t="n">
+        <v>101.7404280841392</v>
       </c>
     </row>
     <row r="119">
@@ -2096,10 +3152,19 @@
         <v>-0.15</v>
       </c>
       <c r="C119" t="n">
+        <v>2.071010891937414</v>
+      </c>
+      <c r="D119" t="n">
         <v>5870.118311813659</v>
       </c>
-      <c r="D119" t="n">
-        <v>2.071010891937414</v>
+      <c r="E119" t="n">
+        <v>120.4085172615302</v>
+      </c>
+      <c r="F119" t="n">
+        <v>9.728665626734713</v>
+      </c>
+      <c r="G119" t="n">
+        <v>103.330648472991</v>
       </c>
     </row>
     <row r="120">
@@ -2110,10 +3175,19 @@
         <v>-0.15</v>
       </c>
       <c r="C120" t="n">
+        <v>1.744616003835776</v>
+      </c>
+      <c r="D120" t="n">
         <v>5765.165509933025</v>
       </c>
-      <c r="D120" t="n">
-        <v>1.744616003835776</v>
+      <c r="E120" t="n">
+        <v>114.9620308287863</v>
+      </c>
+      <c r="F120" t="n">
+        <v>9.497252558418067</v>
+      </c>
+      <c r="G120" t="n">
+        <v>104.9528018806341</v>
       </c>
     </row>
     <row r="121">
@@ -2124,10 +3198,19 @@
         <v>-0.15</v>
       </c>
       <c r="C121" t="n">
+        <v>1.428910877932278</v>
+      </c>
+      <c r="D121" t="n">
         <v>5658.555730496634</v>
       </c>
-      <c r="D121" t="n">
-        <v>1.428910877932278</v>
+      <c r="E121" t="n">
+        <v>109.6310269131789</v>
+      </c>
+      <c r="F121" t="n">
+        <v>9.265013651849699</v>
+      </c>
+      <c r="G121" t="n">
+        <v>106.6097794363905</v>
       </c>
     </row>
     <row r="122">
@@ -2138,10 +3221,19 @@
         <v>-0.15</v>
       </c>
       <c r="C122" t="n">
+        <v>1.124036026348822</v>
+      </c>
+      <c r="D122" t="n">
         <v>5550.258935153612</v>
       </c>
-      <c r="D122" t="n">
-        <v>1.124036026348822</v>
+      <c r="E122" t="n">
+        <v>104.4166943376644</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9.031961990020081</v>
+      </c>
+      <c r="G122" t="n">
+        <v>108.2967953430225</v>
       </c>
     </row>
     <row r="123">
@@ -2152,10 +3244,19 @@
         <v>-0.15</v>
       </c>
       <c r="C123" t="n">
+        <v>0.8303427687709183</v>
+      </c>
+      <c r="D123" t="n">
         <v>5440.239495679376</v>
       </c>
-      <c r="D123" t="n">
-        <v>0.8303427687709183</v>
+      <c r="E123" t="n">
+        <v>99.31826804650595</v>
+      </c>
+      <c r="F123" t="n">
+        <v>8.798101832534813</v>
+      </c>
+      <c r="G123" t="n">
+        <v>110.0194394742357</v>
       </c>
     </row>
     <row r="124">
@@ -2166,10 +3267,19 @@
         <v>-0.15</v>
       </c>
       <c r="C124" t="n">
+        <v>0.5480827944724747</v>
+      </c>
+      <c r="D124" t="n">
         <v>5328.464423742884</v>
       </c>
-      <c r="D124" t="n">
-        <v>0.5480827944724747</v>
+      <c r="E124" t="n">
+        <v>94.3378402725845</v>
+      </c>
+      <c r="F124" t="n">
+        <v>8.563446320506893</v>
+      </c>
+      <c r="G124" t="n">
+        <v>111.7750719364922</v>
       </c>
     </row>
     <row r="125">
@@ -2180,10 +3290,19 @@
         <v>-0.15</v>
       </c>
       <c r="C125" t="n">
+        <v>0.2774302576708865</v>
+      </c>
+      <c r="D125" t="n">
         <v>5214.898814248222</v>
       </c>
-      <c r="D125" t="n">
-        <v>0.2774302576708865</v>
+      <c r="E125" t="n">
+        <v>89.47964802271905</v>
+      </c>
+      <c r="F125" t="n">
+        <v>8.3280074989986</v>
+      </c>
+      <c r="G125" t="n">
+        <v>113.5656094946617</v>
       </c>
     </row>
     <row r="126">
@@ -2194,10 +3313,19 @@
         <v>-0.15</v>
       </c>
       <c r="C126" t="n">
+        <v>0.01862870382165856</v>
+      </c>
+      <c r="D126" t="n">
         <v>5099.51315794711</v>
       </c>
-      <c r="D126" t="n">
-        <v>0.01862870382165856</v>
+      <c r="E126" t="n">
+        <v>84.74555133742892</v>
+      </c>
+      <c r="F126" t="n">
+        <v>8.09181129557515</v>
+      </c>
+      <c r="G126" t="n">
+        <v>115.3856563011122</v>
       </c>
     </row>
     <row r="127">
@@ -2208,10 +3336,19 @@
         <v>-0.15</v>
       </c>
       <c r="C127" t="n">
+        <v>-0.2281482131615798</v>
+      </c>
+      <c r="D127" t="n">
         <v>4982.27377471588</v>
       </c>
-      <c r="D127" t="n">
-        <v>-0.2281482131615798</v>
+      <c r="E127" t="n">
+        <v>80.13358638448422</v>
+      </c>
+      <c r="F127" t="n">
+        <v>7.85487722390123</v>
+      </c>
+      <c r="G127" t="n">
+        <v>117.23938323123</v>
       </c>
     </row>
     <row r="128">
@@ -2222,10 +3359,19 @@
         <v>-0.15</v>
       </c>
       <c r="C128" t="n">
+        <v>-0.4625666437205392</v>
+      </c>
+      <c r="D128" t="n">
         <v>4863.152732268167</v>
       </c>
-      <c r="D128" t="n">
-        <v>-0.4625666437205392</v>
+      <c r="E128" t="n">
+        <v>75.64553068614126</v>
+      </c>
+      <c r="F128" t="n">
+        <v>7.61723844936841</v>
+      </c>
+      <c r="G128" t="n">
+        <v>119.1210424477131</v>
       </c>
     </row>
     <row r="129">
@@ -2236,10 +3382,19 @@
         <v>-0.15</v>
       </c>
       <c r="C129" t="n">
+        <v>-0.6842452505047355</v>
+      </c>
+      <c r="D129" t="n">
         <v>4742.121207469082</v>
       </c>
-      <c r="D129" t="n">
-        <v>-0.6842452505047355</v>
+      <c r="E129" t="n">
+        <v>71.28841536070206</v>
+      </c>
+      <c r="F129" t="n">
+        <v>7.378927532335599</v>
+      </c>
+      <c r="G129" t="n">
+        <v>121.0315247990848</v>
       </c>
     </row>
     <row r="130">
@@ -2250,10 +3405,19 @@
         <v>-0.15</v>
       </c>
       <c r="C130" t="n">
+        <v>-0.8933564238859517</v>
+      </c>
+      <c r="D130" t="n">
         <v>4619.152555361309</v>
       </c>
-      <c r="D130" t="n">
-        <v>-0.8933564238859517</v>
+      <c r="E130" t="n">
+        <v>67.06283773688979</v>
+      </c>
+      <c r="F130" t="n">
+        <v>7.139982453524759</v>
+      </c>
+      <c r="G130" t="n">
+        <v>122.9686521077729</v>
       </c>
     </row>
     <row r="131">
@@ -2264,10 +3428,19 @@
         <v>-0.15</v>
       </c>
       <c r="C131" t="n">
+        <v>-1.089197156050133</v>
+      </c>
+      <c r="D131" t="n">
         <v>4494.224952228841</v>
       </c>
-      <c r="D131" t="n">
-        <v>-1.089197156050133</v>
+      <c r="E131" t="n">
+        <v>62.964334508784</v>
+      </c>
+      <c r="F131" t="n">
+        <v>6.900451067327</v>
+      </c>
+      <c r="G131" t="n">
+        <v>124.927603132468</v>
       </c>
     </row>
     <row r="132">
@@ -2278,10 +3451,19 @@
         <v>-0.15</v>
       </c>
       <c r="C132" t="n">
+        <v>-1.271768972384842</v>
+      </c>
+      <c r="D132" t="n">
         <v>4367.326599341042</v>
       </c>
-      <c r="D132" t="n">
-        <v>-1.271768972384842</v>
+      <c r="E132" t="n">
+        <v>58.99832571965392</v>
+      </c>
+      <c r="F132" t="n">
+        <v>6.660399762831204</v>
+      </c>
+      <c r="G132" t="n">
+        <v>126.8983528877989</v>
       </c>
     </row>
     <row r="133">
@@ -2292,10 +3474,19 @@
         <v>-0.15</v>
       </c>
       <c r="C133" t="n">
+        <v>-1.440614920855592</v>
+      </c>
+      <c r="D133" t="n">
         <v>4238.436268237788</v>
       </c>
-      <c r="D133" t="n">
-        <v>-1.440614920855592</v>
+      <c r="E133" t="n">
+        <v>55.17474907242107</v>
+      </c>
+      <c r="F133" t="n">
+        <v>6.419876525924209</v>
+      </c>
+      <c r="G133" t="n">
+        <v>128.8903311032545</v>
       </c>
     </row>
     <row r="134">
@@ -2306,10 +3497,19 @@
         <v>-0.15</v>
       </c>
       <c r="C134" t="n">
+        <v>-1.595436232242395</v>
+      </c>
+      <c r="D134" t="n">
         <v>4107.563484604553</v>
       </c>
-      <c r="D134" t="n">
-        <v>-1.595436232242395</v>
+      <c r="E134" t="n">
+        <v>51.48600289315596</v>
+      </c>
+      <c r="F134" t="n">
+        <v>6.17898508678488</v>
+      </c>
+      <c r="G134" t="n">
+        <v>130.8727836332346</v>
       </c>
     </row>
     <row r="135">
@@ -2320,10 +3520,19 @@
         <v>-0.1</v>
       </c>
       <c r="C135" t="n">
+        <v>1.732334516257343</v>
+      </c>
+      <c r="D135" t="n">
         <v>3974.696983312842</v>
       </c>
-      <c r="D135" t="n">
-        <v>1.732334516257343</v>
+      <c r="E135" t="n">
+        <v>47.92993509126024</v>
+      </c>
+      <c r="F135" t="n">
+        <v>5.937788595301637</v>
+      </c>
+      <c r="G135" t="n">
+        <v>132.8665012917113</v>
       </c>
     </row>
     <row r="136">
@@ -2334,10 +3543,19 @@
         <v>-0.1</v>
       </c>
       <c r="C136" t="n">
+        <v>1.489024639807993</v>
+      </c>
+      <c r="D136" t="n">
         <v>3839.871957427077</v>
       </c>
-      <c r="D136" t="n">
-        <v>1.489024639807993</v>
+      <c r="E136" t="n">
+        <v>44.52426947429674</v>
+      </c>
+      <c r="F136" t="n">
+        <v>5.69643093633293</v>
+      </c>
+      <c r="G136" t="n">
+        <v>134.8250258857647</v>
       </c>
     </row>
     <row r="137">
@@ -2348,10 +3566,19 @@
         <v>-0.1</v>
       </c>
       <c r="C137" t="n">
+        <v>1.258081980681233</v>
+      </c>
+      <c r="D137" t="n">
         <v>3703.097683393381</v>
       </c>
-      <c r="D137" t="n">
-        <v>1.258081980681233</v>
+      <c r="E137" t="n">
+        <v>41.26543367286968</v>
+      </c>
+      <c r="F137" t="n">
+        <v>5.45500539022844</v>
+      </c>
+      <c r="G137" t="n">
+        <v>136.7742740336962</v>
       </c>
     </row>
     <row r="138">
@@ -2362,10 +3589,19 @@
         <v>-0.1</v>
       </c>
       <c r="C138" t="n">
+        <v>1.041822951347352</v>
+      </c>
+      <c r="D138" t="n">
         <v>3564.438607613153</v>
       </c>
-      <c r="D138" t="n">
-        <v>1.041822951347352</v>
+      <c r="E138" t="n">
+        <v>38.13945907167154</v>
+      </c>
+      <c r="F138" t="n">
+        <v>5.213696680814394</v>
+      </c>
+      <c r="G138" t="n">
+        <v>138.6590757802278</v>
       </c>
     </row>
     <row r="139">
@@ -2376,10 +3612,19 @@
         <v>-0.1</v>
       </c>
       <c r="C139" t="n">
+        <v>0.8380012373073311</v>
+      </c>
+      <c r="D139" t="n">
         <v>3423.946887481813</v>
       </c>
-      <c r="D139" t="n">
-        <v>0.8380012373073311</v>
+      <c r="E139" t="n">
+        <v>35.17111573396529</v>
+      </c>
+      <c r="F139" t="n">
+        <v>4.972660039871144</v>
+      </c>
+      <c r="G139" t="n">
+        <v>140.4917201313401</v>
       </c>
     </row>
     <row r="140">
@@ -2390,10 +3635,19 @@
         <v>-0.1</v>
       </c>
       <c r="C140" t="n">
+        <v>0.6501850308169195</v>
+      </c>
+      <c r="D140" t="n">
         <v>3281.72530623166</v>
       </c>
-      <c r="D140" t="n">
-        <v>0.6501850308169195</v>
+      <c r="E140" t="n">
+        <v>32.36209345674395</v>
+      </c>
+      <c r="F140" t="n">
+        <v>4.73212818743864</v>
+      </c>
+      <c r="G140" t="n">
+        <v>142.2215812501531</v>
       </c>
     </row>
     <row r="141">
@@ -2404,10 +3658,19 @@
         <v>-0.1</v>
       </c>
       <c r="C141" t="n">
+        <v>0.4745937471666245</v>
+      </c>
+      <c r="D141" t="n">
         <v>3137.89105956452</v>
       </c>
-      <c r="D141" t="n">
-        <v>0.4745937471666245</v>
+      <c r="E141" t="n">
+        <v>29.68604970276886</v>
+      </c>
+      <c r="F141" t="n">
+        <v>4.492345702445726</v>
+      </c>
+      <c r="G141" t="n">
+        <v>143.8342466671397</v>
       </c>
     </row>
     <row r="142">
@@ -2418,10 +3681,19 @@
         <v>-0.1</v>
       </c>
       <c r="C142" t="n">
+        <v>0.3166139659304154</v>
+      </c>
+      <c r="D142" t="n">
         <v>2992.617966524852</v>
       </c>
-      <c r="D142" t="n">
-        <v>0.3166139659304154</v>
+      <c r="E142" t="n">
+        <v>27.18130405619889</v>
+      </c>
+      <c r="F142" t="n">
+        <v>4.253636333997026</v>
+      </c>
+      <c r="G142" t="n">
+        <v>145.2730930396683</v>
       </c>
     </row>
     <row r="143">
@@ -2432,10 +3704,19 @@
         <v>-0.1</v>
       </c>
       <c r="C143" t="n">
+        <v>0.1700808826488083</v>
+      </c>
+      <c r="D143" t="n">
         <v>2846.088343325931</v>
       </c>
-      <c r="D143" t="n">
-        <v>0.1700808826488083</v>
+      <c r="E143" t="n">
+        <v>24.84158589731267</v>
+      </c>
+      <c r="F143" t="n">
+        <v>4.016319436500999</v>
+      </c>
+      <c r="G143" t="n">
+        <v>146.5296231989209</v>
       </c>
     </row>
     <row r="144">
@@ -2446,10 +3727,19 @@
         <v>-0.1</v>
       </c>
       <c r="C144" t="n">
+        <v>0.04296703357415892</v>
+      </c>
+      <c r="D144" t="n">
         <v>2698.634254753601</v>
       </c>
-      <c r="D144" t="n">
-        <v>0.04296703357415892</v>
+      <c r="E144" t="n">
+        <v>22.63347381293677</v>
+      </c>
+      <c r="F144" t="n">
+        <v>3.780933283939927</v>
+      </c>
+      <c r="G144" t="n">
+        <v>147.45408857233</v>
       </c>
     </row>
     <row r="145">
@@ -2460,10 +3750,19 @@
         <v>-0.1</v>
       </c>
       <c r="C145" t="n">
+        <v>-0.0738114490315855</v>
+      </c>
+      <c r="D145" t="n">
         <v>2550.466117069661</v>
       </c>
-      <c r="D145" t="n">
-        <v>-0.0738114490315855</v>
+      <c r="E145" t="n">
+        <v>20.62724799948067</v>
+      </c>
+      <c r="F145" t="n">
+        <v>3.547795175159389</v>
+      </c>
+      <c r="G145" t="n">
+        <v>148.1681376839401</v>
       </c>
     </row>
     <row r="146">
@@ -2474,10 +3773,19 @@
         <v>-0.1</v>
       </c>
       <c r="C146" t="n">
+        <v>-0.1700548268932727</v>
+      </c>
+      <c r="D146" t="n">
         <v>2402.236136816471</v>
       </c>
-      <c r="D146" t="n">
-        <v>-0.1700548268932727</v>
+      <c r="E146" t="n">
+        <v>18.76959764357278</v>
+      </c>
+      <c r="F146" t="n">
+        <v>3.317883014298504</v>
+      </c>
+      <c r="G146" t="n">
+        <v>148.2299802531898</v>
       </c>
     </row>
     <row r="147">
@@ -2488,10 +3796,19 @@
         <v>-0.1</v>
       </c>
       <c r="C147" t="n">
+        <v>-0.2562332971041345</v>
+      </c>
+      <c r="D147" t="n">
         <v>2254.071347255844</v>
       </c>
-      <c r="D147" t="n">
-        <v>-0.2562332971041345</v>
+      <c r="E147" t="n">
+        <v>17.06446282321663</v>
+      </c>
+      <c r="F147" t="n">
+        <v>3.091321900264798</v>
+      </c>
+      <c r="G147" t="n">
+        <v>148.164789560627</v>
       </c>
     </row>
     <row r="148">
@@ -2502,10 +3819,19 @@
         <v>-0.1</v>
       </c>
       <c r="C148" t="n">
+        <v>-0.3238582914409317</v>
+      </c>
+      <c r="D148" t="n">
         <v>2107.206033713831</v>
       </c>
-      <c r="D148" t="n">
-        <v>-0.3238582914409317</v>
+      <c r="E148" t="n">
+        <v>15.58126263608797</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2.869884084236422</v>
+      </c>
+      <c r="G148" t="n">
+        <v>146.8653135420132</v>
       </c>
     </row>
     <row r="149">
@@ -2516,10 +3842,19 @@
         <v>-0.1</v>
       </c>
       <c r="C149" t="n">
+        <v>-0.3780994265652067</v>
+      </c>
+      <c r="D149" t="n">
         <v>1961.497172184557</v>
       </c>
-      <c r="D149" t="n">
-        <v>-0.3780994265652067</v>
+      <c r="E149" t="n">
+        <v>14.20944774940251</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2.653210970761234</v>
+      </c>
+      <c r="G149" t="n">
+        <v>145.7088615292739</v>
       </c>
     </row>
     <row r="150">
@@ -2530,10 +3865,19 @@
         <v>-0.1</v>
       </c>
       <c r="C150" t="n">
+        <v>-0.4217170303872965</v>
+      </c>
+      <c r="D150" t="n">
         <v>1819.003470603386</v>
       </c>
-      <c r="D150" t="n">
-        <v>-0.4217170303872965</v>
+      <c r="E150" t="n">
+        <v>13.08538175624671</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2.444166756263994</v>
+      </c>
+      <c r="G150" t="n">
+        <v>142.4937015811711</v>
       </c>
     </row>
     <row r="151">
@@ -2544,10 +3888,19 @@
         <v>-0.1</v>
       </c>
       <c r="C151" t="n">
+        <v>-0.4439957693074538</v>
+      </c>
+      <c r="D151" t="n">
         <v>1679.22012873185</v>
       </c>
-      <c r="D151" t="n">
-        <v>-0.4439957693074538</v>
+      <c r="E151" t="n">
+        <v>12.09729721599555</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2.241780762170292</v>
+      </c>
+      <c r="G151" t="n">
+        <v>139.7833418715359</v>
       </c>
     </row>
     <row r="152">
@@ -2558,10 +3911,19 @@
         <v>-0.1</v>
       </c>
       <c r="C152" t="n">
+        <v>-0.4686110972631434</v>
+      </c>
+      <c r="D152" t="n">
         <v>1544.97681791338</v>
       </c>
-      <c r="D152" t="n">
-        <v>-0.4686110972631434</v>
+      <c r="E152" t="n">
+        <v>11.3145713531632</v>
+      </c>
+      <c r="F152" t="n">
+        <v>2.04986539463459</v>
+      </c>
+      <c r="G152" t="n">
+        <v>134.24331081847</v>
       </c>
     </row>
     <row r="153">
@@ -2572,10 +3934,19 @@
         <v>-0.1</v>
       </c>
       <c r="C153" t="n">
+        <v>-0.4631823977122461</v>
+      </c>
+      <c r="D153" t="n">
         <v>1415.383996051679</v>
       </c>
-      <c r="D153" t="n">
-        <v>-0.4631823977122461</v>
+      <c r="E153" t="n">
+        <v>10.72767563529822</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1.866833572183701</v>
+      </c>
+      <c r="G153" t="n">
+        <v>129.5928218617009</v>
       </c>
     </row>
     <row r="154">
@@ -2586,10 +3957,19 @@
         <v>-0.1</v>
       </c>
       <c r="C154" t="n">
+        <v>-0.4720001324078428</v>
+      </c>
+      <c r="D154" t="n">
         <v>1293.965993965814</v>
       </c>
-      <c r="D154" t="n">
-        <v>-0.4720001324078428</v>
+      <c r="E154" t="n">
+        <v>10.30574012160585</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.697302446595128</v>
+      </c>
+      <c r="G154" t="n">
+        <v>121.4180020858651</v>
       </c>
     </row>
     <row r="155">
@@ -2600,10 +3980,19 @@
         <v>-0.1</v>
       </c>
       <c r="C155" t="n">
+        <v>-0.4514474553277628</v>
+      </c>
+      <c r="D155" t="n">
         <v>1178.536033355913</v>
       </c>
-      <c r="D155" t="n">
-        <v>-0.4514474553277628</v>
+      <c r="E155" t="n">
+        <v>10.12732684235401</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1.537857951093032</v>
+      </c>
+      <c r="G155" t="n">
+        <v>115.4299606099009</v>
       </c>
     </row>
     <row r="156">
@@ -2614,10 +4003,19 @@
         <v>-0.1</v>
       </c>
       <c r="C156" t="n">
+        <v>-0.4370964146455747</v>
+      </c>
+      <c r="D156" t="n">
         <v>1074.097212108165</v>
       </c>
-      <c r="D156" t="n">
-        <v>-0.4370964146455747</v>
+      <c r="E156" t="n">
+        <v>10.01150200305295</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1.395020385446382</v>
+      </c>
+      <c r="G156" t="n">
+        <v>104.4388212477481</v>
       </c>
     </row>
     <row r="157">
@@ -2628,10 +4026,19 @@
         <v>-0.05</v>
       </c>
       <c r="C157" t="n">
+        <v>0.4200630537848637</v>
+      </c>
+      <c r="D157" t="n">
         <v>976.0537718246649</v>
       </c>
-      <c r="D157" t="n">
-        <v>0.4200630537848637</v>
+      <c r="E157" t="n">
+        <v>10</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1.262145651546604</v>
+      </c>
+      <c r="G157" t="n">
+        <v>98.0434402835001</v>
       </c>
     </row>
     <row r="158">
@@ -2642,10 +4049,19 @@
         <v>-0.1</v>
       </c>
       <c r="C158" t="n">
+        <v>-0.3804166497723249</v>
+      </c>
+      <c r="D158" t="n">
         <v>888.84094055679</v>
       </c>
-      <c r="D158" t="n">
-        <v>-0.3804166497723249</v>
+      <c r="E158" t="n">
+        <v>10</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1.144924658062767</v>
+      </c>
+      <c r="G158" t="n">
+        <v>87.21283126787489</v>
       </c>
     </row>
     <row r="159">
@@ -2656,10 +4072,19 @@
         <v>-0.05</v>
       </c>
       <c r="C159" t="n">
+        <v>0.3295004338208976</v>
+      </c>
+      <c r="D159" t="n">
         <v>811.5550179263576</v>
       </c>
-      <c r="D159" t="n">
-        <v>0.3295004338208976</v>
+      <c r="E159" t="n">
+        <v>10</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1.041804825434136</v>
+      </c>
+      <c r="G159" t="n">
+        <v>77.28592263043242</v>
       </c>
     </row>
     <row r="160">
@@ -2670,10 +4095,19 @@
         <v>-0.05</v>
       </c>
       <c r="C160" t="n">
+        <v>0.2740586366068081</v>
+      </c>
+      <c r="D160" t="n">
         <v>740.103232176065</v>
       </c>
-      <c r="D160" t="n">
-        <v>0.2740586366068081</v>
+      <c r="E160" t="n">
+        <v>10</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.9470981596954599</v>
+      </c>
+      <c r="G160" t="n">
+        <v>71.45178575029252</v>
       </c>
     </row>
     <row r="161">
@@ -2684,10 +4118,19 @@
         <v>-0.05</v>
       </c>
       <c r="C161" t="n">
+        <v>0.2613316290354692</v>
+      </c>
+      <c r="D161" t="n">
         <v>624.0304114699072</v>
       </c>
-      <c r="D161" t="n">
-        <v>0.2613316290354692</v>
+      <c r="E161" t="n">
+        <v>10</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.7945191231558092</v>
+      </c>
+      <c r="G161" t="n">
+        <v>116.0728207061578</v>
       </c>
     </row>
     <row r="162">
@@ -2698,10 +4141,19 @@
         <v>-0.05</v>
       </c>
       <c r="C162" t="n">
+        <v>0.1702222740937616</v>
+      </c>
+      <c r="D162" t="n">
         <v>533.0777947219906</v>
       </c>
-      <c r="D162" t="n">
-        <v>0.1702222740937616</v>
+      <c r="E162" t="n">
+        <v>10</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.67604903614557</v>
+      </c>
+      <c r="G162" t="n">
+        <v>90.95261674791664</v>
       </c>
     </row>
     <row r="163">
@@ -2712,10 +4164,19 @@
         <v>-0.05</v>
       </c>
       <c r="C163" t="n">
+        <v>0.1731284062484593</v>
+      </c>
+      <c r="D163" t="n">
         <v>430.1299032401924</v>
       </c>
-      <c r="D163" t="n">
-        <v>0.1731284062484593</v>
+      <c r="E163" t="n">
+        <v>10</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.5430967529111456</v>
+      </c>
+      <c r="G163" t="n">
+        <v>102.9478914817982</v>
       </c>
     </row>
     <row r="164">
@@ -2726,10 +4187,111 @@
         <v>-0.05</v>
       </c>
       <c r="C164" t="n">
+        <v>0.1298834349592644</v>
+      </c>
+      <c r="D164" t="n">
         <v>340.905185165166</v>
       </c>
-      <c r="D164" t="n">
-        <v>0.1298834349592644</v>
+      <c r="E164" t="n">
+        <v>10</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.4288408799661523</v>
+      </c>
+      <c r="G164" t="n">
+        <v>89.22471807502637</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="B165" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.05759977431869386</v>
+      </c>
+      <c r="D165" t="n">
+        <v>254.5175296552962</v>
+      </c>
+      <c r="E165" t="n">
+        <v>10</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.3190838187897792</v>
+      </c>
+      <c r="G165" t="n">
+        <v>86.38765550986983</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="B166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.03586506947619218</v>
+      </c>
+      <c r="D166" t="n">
+        <v>172.8073447745236</v>
+      </c>
+      <c r="E166" t="n">
+        <v>10</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.2160780629686084</v>
+      </c>
+      <c r="G166" t="n">
+        <v>81.71018488077257</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="B167" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.03117244163981478</v>
+      </c>
+      <c r="D167" t="n">
+        <v>91.71618982876933</v>
+      </c>
+      <c r="E167" t="n">
+        <v>10</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.1147688254200615</v>
+      </c>
+      <c r="G167" t="n">
+        <v>81.09115494575428</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>-15</v>
+      </c>
+      <c r="B168" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.01479837247583625</v>
+      </c>
+      <c r="D168" t="n">
+        <v>37.36638195158394</v>
+      </c>
+      <c r="E168" t="n">
+        <v>10</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.04800809834012187</v>
+      </c>
+      <c r="G168" t="n">
+        <v>54.34980787718539</v>
       </c>
     </row>
   </sheetData>
